--- a/InputData/indst/FIEF/Feasible Industrial Equipment Fuels.xlsx
+++ b/InputData/indst/FIEF/Feasible Industrial Equipment Fuels.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\US\eps-us\InputData\indst\FIEF\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96A3BB2F-0E13-4098-9BD6-3417573273C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EDD2ADA1-0AE2-4CE7-90B1-0186DADBC3E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11235" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="77">
   <si>
     <t>FIEF Feasible Industrial Equipment Fuels</t>
   </si>
@@ -58,9 +58,6 @@
     <t>https://github.com/EnergyInnovation/eps-us</t>
   </si>
   <si>
-    <t>Rule: a fuel observed serving a process in ANY of the 25 modeled industries is treated as technically feasible for that process in all industries (zero observed share elsewhere is a corner solution; not physical impossibility). This covers 66 of the 96 feasible cells. The remaining judgment cells are documented on the Mask tab and below.</t>
-  </si>
-  <si>
     <t>Hydrogen combustion equipment across industrial temperature ranges (judgment cells)</t>
   </si>
   <si>
@@ -121,15 +118,9 @@
     <t>Judgment cells</t>
   </si>
   <si>
-    <t>30 of the 96 feasible cells are engineering judgment rather than observed use: hydrogen; green hydrogen; and low carbon hydrogen (9 processes each; all but cooling and lighting) and district heat (heat below 100 C; heat 100 to 200 C; facility HVAC). All other feasible cells follow the observed-anywhere rule; all other zero cells are physical or practical infeasibility (e.g. only electricity serves lighting).</t>
-  </si>
-  <si>
     <t>Floor eligibility</t>
   </si>
   <si>
-    <t>The exported mask equals technical feasibility TIMES a floor-eligibility flag per fuel (Mask tab column N). Only electricity; purchased heat; and the three hydrogen fuels receive the epsilon floor. Validation runs with the floor applied to ALL feasible fuels showed cheap conventional fuels (biomass +34%; hard coal +18% in 2050 BAU fuel use at epsilon=0.001) breaking through at BAU prices in industries whose zero calibrated share reflects non-cost barriers (fuel handling; supply logistics) - a BAU distortion with no policy-analysis benefit. Restricting the floor to the policy-relevant locked-out fuels preserves BAU (conventional zeros stay hard) while unlocking clean-fuel deployment under financial policy. The full technical-feasibility matrix remains documented on the Mask tab.</t>
-  </si>
-  <si>
     <t>Parameter</t>
   </si>
   <si>
@@ -223,12 +214,6 @@
     <t>observed + judgment: hydrogen heat/machine drive</t>
   </si>
   <si>
-    <t>green hydrogen if</t>
-  </si>
-  <si>
-    <t>low carbon hydrogen if</t>
-  </si>
-  <si>
     <t>Parity cost-advantage threshold (= (1/eps)^(1/exponent))</t>
   </si>
   <si>
@@ -250,18 +235,12 @@
     <t>Status</t>
   </si>
   <si>
-    <t>Count of 0/1 cells equals 132 (12 fuels x 11 processes)</t>
-  </si>
-  <si>
     <t>Electricity row (Mask row 2) is all 1</t>
   </si>
   <si>
     <t>Facility lighting column (Mask col L) sums to 1 (electricity only)</t>
   </si>
   <si>
-    <t>Feasible-cell count equals 96</t>
-  </si>
-  <si>
     <t>Epsilon (Parameters!B2) is between 0 and 0.1</t>
   </si>
   <si>
@@ -275,6 +254,21 @@
   </si>
   <si>
     <t>Feasible Industrial Equipment Fuels</t>
+  </si>
+  <si>
+    <t>Count of 0/1 cells equals 110 (10 fuels x 11 processes)</t>
+  </si>
+  <si>
+    <t>Feasible-cell count equals 78</t>
+  </si>
+  <si>
+    <t>Rule: a fuel observed serving a process in ANY of the 25 modeled industries is treated as technically feasible for that process in all industries (zero observed share elsewhere is a corner solution; not physical impossibility). This covers 66 of the 78 feasible cells. The remaining judgment cells are documented on the Mask tab and below.</t>
+  </si>
+  <si>
+    <t>12 of the 78 feasible cells are engineering judgment rather than observed use: hydrogen (9 processes; all but cooling and lighting) and district heat (heat below 100 C; heat 100 to 200 C; facility HVAC). All other feasible cells follow the observed-anywhere rule; all other zero cells are physical or practical infeasibility (e.g. only electricity serves lighting).</t>
+  </si>
+  <si>
+    <t>The exported mask equals technical feasibility TIMES a floor-eligibility flag per fuel (Mask tab column N). Only electricity; purchased heat; and hydrogen receive the epsilon floor. Validation runs with the floor applied to ALL feasible fuels showed cheap conventional fuels (biomass +34%; hard coal +18% in 2050 BAU fuel use at epsilon=0.001) breaking through at BAU prices in industries whose zero calibrated share reflects non-cost barriers (fuel handling; supply logistics) - a BAU distortion with no policy-analysis benefit. Restricting the floor to the policy-relevant locked-out fuels preserves BAU (conventional zeros stay hard) while unlocking clean-fuel deployment under financial policy. The full technical-feasibility matrix remains documented on the Mask tab.</t>
   </si>
 </sst>
 </file>
@@ -648,18 +642,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B31"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
     <col min="2" max="2" width="110" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -667,142 +661,142 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B4" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B5" s="3" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B6" s="3">
         <v>2026</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="B8" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B10" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B10" s="2" t="s">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B11" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B11" s="3" t="s">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B12" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B12" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B13" s="3">
         <v>2022</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B14" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+      <c r="B15" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="B15" s="3" t="s">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B17" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B17" s="2" t="s">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B18" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B18" s="3" t="s">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B19" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B19" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B20" s="3">
         <v>2024</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B21" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="B22" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="B22" s="3" t="s">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A25" s="1" t="s">
+    <row r="26" spans="1:2" ht="60" x14ac:dyDescent="0.25">
+      <c r="A26" s="5" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A26" s="5" t="s">
+      <c r="B26" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B26" s="3" t="s">
+    </row>
+    <row r="27" spans="1:2" ht="60" x14ac:dyDescent="0.25">
+      <c r="A27" s="5" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" ht="58" x14ac:dyDescent="0.35">
-      <c r="A27" s="5" t="s">
+      <c r="B27" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B27" s="3" t="s">
+    </row>
+    <row r="28" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A28" s="5" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="28" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A28" s="5" t="s">
+      <c r="B28" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B28" s="3" t="s">
+    </row>
+    <row r="29" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A29" s="5" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="29" spans="1:2" ht="29" x14ac:dyDescent="0.35">
-      <c r="A29" s="5" t="s">
+      <c r="B29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B29" s="3" t="s">
+    </row>
+    <row r="30" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+      <c r="A30" s="5" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="30" spans="1:2" ht="58" x14ac:dyDescent="0.35">
-      <c r="A30" s="5" t="s">
+      <c r="B30" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="105" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" ht="101.5" x14ac:dyDescent="0.35">
-      <c r="A31" s="1" t="s">
-        <v>28</v>
-      </c>
       <c r="B31" s="3" t="s">
-        <v>29</v>
+        <v>76</v>
       </c>
     </row>
   </sheetData>
@@ -818,31 +812,31 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="45" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="B2">
         <v>1E-3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B3">
         <v>6</v>
@@ -855,631 +849,543 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:N22"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:N20"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="12" width="16" customWidth="1"/>
     <col min="13" max="13" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="87" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" ht="90" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="N1" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="L1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2" t="s">
         <v>46</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="N2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+      <c r="M3" t="s">
+        <v>46</v>
+      </c>
+      <c r="N3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>1</v>
-      </c>
-      <c r="M2" t="s">
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4" t="s">
+        <v>46</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="N2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <v>0</v>
+      </c>
+      <c r="M5" t="s">
+        <v>46</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>0</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="K3">
-        <v>0</v>
-      </c>
-      <c r="L3">
-        <v>1</v>
-      </c>
-      <c r="M3" t="s">
-        <v>49</v>
-      </c>
-      <c r="N3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A4" s="1" t="s">
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>0</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6" t="s">
+        <v>46</v>
+      </c>
+      <c r="N6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>0</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4" t="s">
-        <v>49</v>
-      </c>
-      <c r="N4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A5" s="1" t="s">
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>0</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <v>0</v>
+      </c>
+      <c r="L7">
+        <v>0</v>
+      </c>
+      <c r="M7" t="s">
         <v>52</v>
       </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="G5">
-        <v>0</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-      <c r="J5">
-        <v>0</v>
-      </c>
-      <c r="K5">
-        <v>0</v>
-      </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5" t="s">
-        <v>49</v>
-      </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A6" s="1" t="s">
+      <c r="N7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>1</v>
-      </c>
-      <c r="J6">
-        <v>1</v>
-      </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-      <c r="L6">
-        <v>1</v>
-      </c>
-      <c r="M6" t="s">
-        <v>49</v>
-      </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A7" s="1" t="s">
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>1</v>
+      </c>
+      <c r="M8" t="s">
+        <v>46</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B7">
-        <v>0</v>
-      </c>
-      <c r="C7">
-        <v>0</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>0</v>
-      </c>
-      <c r="F7">
-        <v>0</v>
-      </c>
-      <c r="G7">
-        <v>0</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-      <c r="J7">
-        <v>1</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7" t="s">
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>1</v>
+      </c>
+      <c r="M9" t="s">
+        <v>46</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="N7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A8" s="1" t="s">
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+      <c r="I10">
+        <v>1</v>
+      </c>
+      <c r="J10">
+        <v>1</v>
+      </c>
+      <c r="K10">
+        <v>0</v>
+      </c>
+      <c r="L10">
+        <v>1</v>
+      </c>
+      <c r="M10" t="s">
+        <v>46</v>
+      </c>
+      <c r="N10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-      <c r="C8">
-        <v>1</v>
-      </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-      <c r="E8">
-        <v>1</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
-      <c r="G8">
-        <v>0</v>
-      </c>
-      <c r="H8">
-        <v>1</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-      <c r="J8">
-        <v>0</v>
-      </c>
-      <c r="K8">
-        <v>0</v>
-      </c>
-      <c r="L8">
-        <v>1</v>
-      </c>
-      <c r="M8" t="s">
-        <v>49</v>
-      </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A9" s="1" t="s">
+      <c r="B11">
+        <v>0</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11" t="s">
         <v>57</v>
       </c>
-      <c r="B9">
-        <v>1</v>
-      </c>
-      <c r="C9">
-        <v>1</v>
-      </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
-      <c r="E9">
-        <v>1</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>1</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="K9">
-        <v>0</v>
-      </c>
-      <c r="L9">
-        <v>1</v>
-      </c>
-      <c r="M9" t="s">
-        <v>49</v>
-      </c>
-      <c r="N9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A10" s="1" t="s">
+      <c r="N11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="B10">
-        <v>1</v>
-      </c>
-      <c r="C10">
-        <v>1</v>
-      </c>
-      <c r="D10">
-        <v>1</v>
-      </c>
-      <c r="E10">
-        <v>1</v>
-      </c>
-      <c r="F10">
-        <v>1</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10">
-        <v>1</v>
-      </c>
-      <c r="I10">
-        <v>1</v>
-      </c>
-      <c r="J10">
-        <v>1</v>
-      </c>
-      <c r="K10">
-        <v>0</v>
-      </c>
-      <c r="L10">
-        <v>1</v>
-      </c>
-      <c r="M10" t="s">
-        <v>49</v>
-      </c>
-      <c r="N10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A11" s="1" t="s">
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>59</v>
       </c>
-      <c r="B11">
-        <v>0</v>
-      </c>
-      <c r="C11">
-        <v>0</v>
-      </c>
-      <c r="D11">
-        <v>1</v>
-      </c>
-      <c r="E11">
-        <v>1</v>
-      </c>
-      <c r="F11">
-        <v>1</v>
-      </c>
-      <c r="G11">
-        <v>0</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <v>0</v>
-      </c>
-      <c r="L11">
-        <v>0</v>
-      </c>
-      <c r="M11" t="s">
+      <c r="B15" t="s">
         <v>60</v>
       </c>
-      <c r="N11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A12" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B12">
-        <v>0</v>
-      </c>
-      <c r="C12">
-        <v>0</v>
-      </c>
-      <c r="D12">
-        <v>1</v>
-      </c>
-      <c r="E12">
-        <v>1</v>
-      </c>
-      <c r="F12">
-        <v>1</v>
-      </c>
-      <c r="G12">
-        <v>0</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12">
-        <v>0</v>
-      </c>
-      <c r="L12">
-        <v>0</v>
-      </c>
-      <c r="M12" t="s">
-        <v>60</v>
-      </c>
-      <c r="N12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A13" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B13">
-        <v>0</v>
-      </c>
-      <c r="C13">
-        <v>0</v>
-      </c>
-      <c r="D13">
-        <v>1</v>
-      </c>
-      <c r="E13">
-        <v>1</v>
-      </c>
-      <c r="F13">
-        <v>1</v>
-      </c>
-      <c r="G13">
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <v>0</v>
-      </c>
-      <c r="L13">
-        <v>0</v>
-      </c>
-      <c r="M13" t="s">
-        <v>60</v>
-      </c>
-      <c r="N13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A16" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>64</v>
-      </c>
-      <c r="B17" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>1E-4</v>
+      </c>
+      <c r="B16">
+        <f>(1/A16)^(1/Parameters!$B$3)</f>
+        <v>4.6415888336127793</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>1E-3</v>
+      </c>
+      <c r="B17">
+        <f>(1/A17)^(1/Parameters!$B$3)</f>
+        <v>3.1622776601683791</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18">
-        <v>1E-4</v>
+        <v>0.01</v>
       </c>
       <c r="B18">
         <f>(1/A18)^(1/Parameters!$B$3)</f>
-        <v>4.6415888336127793</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A19">
-        <v>1E-3</v>
-      </c>
-      <c r="B19">
-        <f>(1/A19)^(1/Parameters!$B$3)</f>
-        <v>3.1622776601683791</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A20">
-        <v>0.01</v>
+        <v>2.1544346900318838</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>61</v>
       </c>
       <c r="B20">
-        <f>(1/A20)^(1/Parameters!$B$3)</f>
-        <v>2.1544346900318838</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
-        <v>66</v>
-      </c>
-      <c r="B22">
         <f>(1/Parameters!$B$2)^(1/Parameters!$B$3)</f>
         <v>3.1622776601683791</v>
       </c>
@@ -1492,40 +1398,40 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="60" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B2">
-        <f>COUNTIF(Mask!B2:L13,0)+COUNTIF(Mask!B2:L13,1)</f>
-        <v>132</v>
+        <f>COUNTIF(Mask!B2:L11,0)+COUNTIF(Mask!B2:L11,1)</f>
+        <v>110</v>
       </c>
       <c r="C2" t="str">
-        <f>IF(B2=132,"PASS","FAIL")</f>
+        <f>IF(B2=110,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="B3">
         <f>SUM(Mask!B2:L2)</f>
@@ -1536,12 +1442,12 @@
         <v>PASS</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="B4">
-        <f>SUM(Mask!L2:L13)</f>
+        <f>SUM(Mask!L2:L11)</f>
         <v>7</v>
       </c>
       <c r="C4" t="str">
@@ -1549,22 +1455,22 @@
         <v>FAIL</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>73</v>
       </c>
       <c r="B5">
-        <f>SUM(Mask!B2:L13)</f>
-        <v>76</v>
+        <f>SUM(Mask!B2:L11)</f>
+        <v>70</v>
       </c>
       <c r="C5" t="str">
-        <f>IF(B5=96,"PASS","FAIL")</f>
+        <f>IF(B5=78,"PASS","FAIL")</f>
         <v>FAIL</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="B6">
         <f>IF(AND(Parameters!$B$2&gt;0,Parameters!$B$2&lt;0.1),1,0)</f>
@@ -1585,50 +1491,50 @@
   <sheetPr>
     <tabColor rgb="FF1F3864"/>
   </sheetPr>
-  <dimension ref="A1:L13"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:L11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="B1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" t="s">
         <v>35</v>
       </c>
-      <c r="C1" t="s">
+      <c r="F1" t="s">
         <v>36</v>
       </c>
-      <c r="D1" t="s">
+      <c r="G1" t="s">
         <v>37</v>
       </c>
-      <c r="E1" t="s">
+      <c r="H1" t="s">
         <v>38</v>
       </c>
-      <c r="F1" t="s">
+      <c r="I1" t="s">
         <v>39</v>
       </c>
-      <c r="G1" t="s">
+      <c r="J1" t="s">
         <v>40</v>
       </c>
-      <c r="H1" t="s">
+      <c r="K1" t="s">
         <v>41</v>
       </c>
-      <c r="I1" t="s">
+      <c r="L1" t="s">
         <v>42</v>
       </c>
-      <c r="J1" t="s">
-        <v>43</v>
-      </c>
-      <c r="K1" t="s">
-        <v>44</v>
-      </c>
-      <c r="L1" t="s">
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
         <v>45</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>48</v>
       </c>
       <c r="B2">
         <f>Mask!B2*Mask!$N2</f>
@@ -1675,9 +1581,9 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="B3">
         <f>Mask!B3*Mask!$N3</f>
@@ -1724,9 +1630,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="B4">
         <f>Mask!B4*Mask!$N4</f>
@@ -1773,9 +1679,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="B5">
         <f>Mask!B5*Mask!$N5</f>
@@ -1822,9 +1728,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B6">
         <f>Mask!B6*Mask!$N6</f>
@@ -1871,9 +1777,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="B7">
         <f>Mask!B7*Mask!$N7</f>
@@ -1920,9 +1826,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B8">
         <f>Mask!B8*Mask!$N8</f>
@@ -1969,9 +1875,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B9">
         <f>Mask!B9*Mask!$N9</f>
@@ -2018,9 +1924,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B10">
         <f>Mask!B10*Mask!$N10</f>
@@ -2067,9 +1973,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="B11">
         <f>Mask!B11*Mask!$N11</f>
@@ -2113,104 +2019,6 @@
       </c>
       <c r="L11">
         <f>Mask!L11*Mask!$N11</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>61</v>
-      </c>
-      <c r="B12">
-        <f>Mask!B12*Mask!$N12</f>
-        <v>0</v>
-      </c>
-      <c r="C12">
-        <f>Mask!C12*Mask!$N12</f>
-        <v>0</v>
-      </c>
-      <c r="D12">
-        <f>Mask!D12*Mask!$N12</f>
-        <v>1</v>
-      </c>
-      <c r="E12">
-        <f>Mask!E12*Mask!$N12</f>
-        <v>1</v>
-      </c>
-      <c r="F12">
-        <f>Mask!F12*Mask!$N12</f>
-        <v>1</v>
-      </c>
-      <c r="G12">
-        <f>Mask!G12*Mask!$N12</f>
-        <v>0</v>
-      </c>
-      <c r="H12">
-        <f>Mask!H12*Mask!$N12</f>
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <f>Mask!I12*Mask!$N12</f>
-        <v>0</v>
-      </c>
-      <c r="J12">
-        <f>Mask!J12*Mask!$N12</f>
-        <v>0</v>
-      </c>
-      <c r="K12">
-        <f>Mask!K12*Mask!$N12</f>
-        <v>0</v>
-      </c>
-      <c r="L12">
-        <f>Mask!L12*Mask!$N12</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>62</v>
-      </c>
-      <c r="B13">
-        <f>Mask!B13*Mask!$N13</f>
-        <v>0</v>
-      </c>
-      <c r="C13">
-        <f>Mask!C13*Mask!$N13</f>
-        <v>0</v>
-      </c>
-      <c r="D13">
-        <f>Mask!D13*Mask!$N13</f>
-        <v>1</v>
-      </c>
-      <c r="E13">
-        <f>Mask!E13*Mask!$N13</f>
-        <v>1</v>
-      </c>
-      <c r="F13">
-        <f>Mask!F13*Mask!$N13</f>
-        <v>1</v>
-      </c>
-      <c r="G13">
-        <f>Mask!G13*Mask!$N13</f>
-        <v>0</v>
-      </c>
-      <c r="H13">
-        <f>Mask!H13*Mask!$N13</f>
-        <v>0</v>
-      </c>
-      <c r="I13">
-        <f>Mask!I13*Mask!$N13</f>
-        <v>0</v>
-      </c>
-      <c r="J13">
-        <f>Mask!J13*Mask!$N13</f>
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <f>Mask!K13*Mask!$N13</f>
-        <v>0</v>
-      </c>
-      <c r="L13">
-        <f>Mask!L13*Mask!$N13</f>
         <v>0</v>
       </c>
     </row>
@@ -2225,19 +2033,19 @@
     <tabColor rgb="FF1F3864"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="B1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="B2">
         <f>Parameters!$B$2</f>
